--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/OKLAHOMA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/OKLAHOMA_2022.xlsx
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C139">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C208">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C216">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C479">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C504">
@@ -13207,7 +13207,7 @@
         <v>44</v>
       </c>
       <c r="D714">
-        <v>0.009232060428031893</v>
+        <v>0.009232060428031891</v>
       </c>
     </row>
     <row r="715">
